--- a/тест-сьют.xlsx
+++ b/тест-сьют.xlsx
@@ -8,20 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestProjectIntern_n1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{473197A1-76EE-4306-9025-A246FE911FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE41CB32-093F-4F3B-81E0-AF0898A28374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тест-кейс №1" sheetId="4" r:id="rId1"/>
     <sheet name="Тест-кейс №2" sheetId="8" r:id="rId2"/>
     <sheet name="Тест-кейс №3" sheetId="11" r:id="rId3"/>
     <sheet name="Тест-кейс №4" sheetId="13" r:id="rId4"/>
-    <sheet name="Тест-кейс №5" sheetId="14" r:id="rId5"/>
-    <sheet name="Тест-кейс №6" sheetId="16" r:id="rId6"/>
-    <sheet name="Тест-кейс №4 (3)" sheetId="15" r:id="rId7"/>
-    <sheet name="Лист2" sheetId="9" r:id="rId8"/>
-    <sheet name="Лист1" sheetId="12" r:id="rId9"/>
+    <sheet name="Тест-кейс №5" sheetId="16" r:id="rId5"/>
+    <sheet name="Лист2" sheetId="9" r:id="rId6"/>
+    <sheet name="Лист1" sheetId="12" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
   <si>
     <t>Название:</t>
   </si>
@@ -288,20 +286,7 @@
     <t>POST запрос со статусом 200, токен получен</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Вызвать endpoint POST 
-https://itester.online/api/accounts
-с cookie X-iTester-Access: 2ad3f9a0ee6b486db902ade89d6850ff </t>
-  </si>
-  <si>
     <t>POST запрос со статусом 200 , в body будет пустая коллекция</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Вызвать endpoint POST 
-https://itester.online/api/cards/orders с cookie X-iTester-Access: 2ad3f9a0ee6b486db902ade89d6850ff </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Вызвать endpoint POST 
-https://itester.online/api/cards с cookie X-iTester-Access: 2ad3f9a0ee6b486db902ade89d6850ff </t>
   </si>
   <si>
     <t>Авторизация пользователя(Web-Api,негативный сценарий)</t>
@@ -367,57 +352,6 @@
   </si>
   <si>
     <t>POST запрос со статусом 400, токен получен</t>
-  </si>
-  <si>
-    <r>
-      <t>В системе</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> не должно</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> быть </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="8" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>login, email</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  пользователя, то есть пользователь не должен быть зарегистрирован</t>
-    </r>
   </si>
   <si>
     <r>
@@ -480,14 +414,56 @@
     <t xml:space="preserve">Сookie X-iTester-Access: 2ad3f9a0ee6b486db902ade89d6850ff </t>
   </si>
   <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/api/operations с body состоящим из {"operationCode":"AccountOpen"}</t>
+  </si>
+  <si>
+    <t>2. Вызвать endpoint PUTCH https://itester.online/api/operations?requestId (requestId берем из PUT запроса) с body состоящим из [
+    {"identifier":"AccountType","value":"string"},{"identifier":"Currency","value":"string"},{"identifier":"LastName","value":"string"},{"identifier":"FirstName","value":"string"},{"identifier":"MiddleName","value":"string"},{"identifier":"Birthdate","value":"string"}
+]</t>
+  </si>
+  <si>
+    <t>3. Вызвать endpoint POST https://itester.online/api/operations?requestId (requestId берем из PUT запроса)</t>
+  </si>
+  <si>
+    <t>Текущий счет</t>
+  </si>
+  <si>
+    <t>Накопительный счет</t>
+  </si>
+  <si>
+    <t>Руб</t>
+  </si>
+  <si>
+    <t>Евро</t>
+  </si>
+  <si>
+    <t>Доллары</t>
+  </si>
+  <si>
+    <t>Юани</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Вызвать endpoint GET 
+https://itester.online/api/accounts
+с cookie X-iTester-Access: 2ad3f9a0ee6b486db902ade89d6850ff </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Вызвать endpoint GET
+https://itester.online/api/cards с cookie X-iTester-Access: 2ad3f9a0ee6b486db902ade89d6850ff </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Вызвать endpoint GET 
+https://itester.online/api/cards/orders с cookie X-iTester-Access: 2ad3f9a0ee6b486db902ade89d6850ff </t>
+  </si>
+  <si>
     <t>PUT запрос со статусом 200, получен response объект:{
   "clientId": 0,
-  "isConfirmed": true,
-  "isFinished": true,
+  "isConfirmed": false,
+  "isFinished": false,
   "name": "string",
   "operationCode": "AccountOpen",
   "requestId": 0,
-  "startDate": "2026-04-06T11:20:21.698Z",
+  "startDate": "string",
   "stepId": 0,
   "stepParams": [
     {
@@ -509,19 +485,6 @@
 }</t>
   </si>
   <si>
-    <t>1. Вызвать endpoint PUT https://itester.online/api/operations с body состоящим из {"operationCode":"AccountOpen"}</t>
-  </si>
-  <si>
-    <t>2. Вызвать endpoint PUTCH https://itester.online/api/operations?requestId (requestId берем из PUT запроса) с body состоящим из [
-    {"identifier":"AccountType","value":"string"},{"identifier":"Currency","value":"Российский Рубль"},{"identifier":"LastName","value":"lastname"},{"identifier":"FirstName","value":"name"},{"identifier":"MiddleName","value":"Владимирович"},{"identifier":"Birthdate","value":"2000-01-01"}
-]</t>
-  </si>
-  <si>
-    <t>2. Вызвать endpoint PUTCH https://itester.online/api/operations?requestId (requestId берем из PUT запроса) с body состоящим из [
-    {"identifier":"AccountType","value":"string"},{"identifier":"Currency","value":"string"},{"identifier":"LastName","value":"string"},{"identifier":"FirstName","value":"string"},{"identifier":"MiddleName","value":"string"},{"identifier":"Birthdate","value":"string"}
-]</t>
-  </si>
-  <si>
     <t>PUTCH запрос со статусом 200, получен response объект:{
   "clientId": 0,
   "isConfirmed": false,
@@ -529,42 +492,10 @@
   "name": "string",
   "operationCode": "AccountOpen",
   "requestId": 0,
-  "startDate": "2026-04-06T11:20:21.698Z",
+  "startDate": "string",
   "stepId": 0,
   "stepParams": null
 }</t>
-  </si>
-  <si>
-    <t>PUT запрос со статусом 200, получен response объект:{
-  "clientId": 0,
-  "isConfirmed": false,
-  "isFinished": false,
-  "name": "string",
-  "operationCode": "AccountOpen",
-  "requestId": 0,
-  "startDate": "2026-04-06T11:20:21.698Z",
-  "stepId": 0,
-  "stepParams": [
-    {
-      "identifier": "string",
-      "value": "string",
-      "name": "string",
-      "requirements": {
-        "mask": "string",
-        "max": 0,
-        "min": 0,
-        "required": true
-      },
-      "type": "string",
-      "values": [
-        "string"
-      ]
-    }
-  ]
-}</t>
-  </si>
-  <si>
-    <t>3. Вызвать endpoint POST https://itester.online/api/operations?requestId (requestId берем из PUT запроса)</t>
   </si>
   <si>
     <t>POST запрос со статусом 200, получен response объект:{
@@ -574,28 +505,19 @@
   "name": "string",
   "operationCode": "AccountOpen",
   "requestId": 0,
-  "startDate": "2026-04-06T11:20:21.698Z",
+  "startDate": "string",
   "stepId": 0,
   "stepParams": null
 }</t>
   </si>
   <si>
-    <t>Текущий счет</t>
-  </si>
-  <si>
-    <t>Накопительный счет</t>
-  </si>
-  <si>
-    <t>Руб</t>
-  </si>
-  <si>
-    <t>Евро</t>
-  </si>
-  <si>
-    <t>Доллары</t>
-  </si>
-  <si>
-    <t>Юани</t>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>0,01</t>
+  </si>
+  <si>
+    <t>-0,01</t>
   </si>
 </sst>
 </file>
@@ -889,7 +811,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1088,6 +1010,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1915,7 +1838,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C7" s="42"/>
       <c r="D7" s="43"/>
@@ -1994,30 +1917,30 @@
     </row>
     <row r="16" spans="1:5" ht="144.75" customHeight="1">
       <c r="A16" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="31" t="s">
         <v>64</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>65</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="127.5" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="31"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="88.5" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="B18" s="31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C18" s="31"/>
       <c r="D18" s="3"/>
@@ -2109,7 +2032,7 @@
         <v>12</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C1" s="58"/>
       <c r="D1" s="59"/>
@@ -2120,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C2" s="60"/>
       <c r="D2" s="60"/>
@@ -2177,7 +2100,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C7" s="42"/>
       <c r="D7" s="43"/>
@@ -2249,7 +2172,7 @@
         <v>62</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C15" s="31"/>
       <c r="D15" s="2"/>
@@ -2343,260 +2266,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C499E148-B69F-4B85-B89E-1661347B9B98}">
-  <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="34.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="51.42578125" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="57" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" ht="49.5" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="60" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" ht="36" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A4" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" ht="75.75" customHeight="1">
-      <c r="A5" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" ht="29.1" customHeight="1">
-      <c r="A6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" ht="39.75" customHeight="1">
-      <c r="A7" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" ht="26.1" customHeight="1">
-      <c r="A8" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A9" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
-    </row>
-    <row r="10" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A10" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="27" customHeight="1">
-      <c r="A13" s="40"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="27" customHeight="1">
-      <c r="A14" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="1:5" ht="409.5" customHeight="1">
-      <c r="A15" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" ht="296.25" customHeight="1">
-      <c r="A16" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" ht="127.5" customHeight="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" ht="88.5" customHeight="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="3"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="16"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="16"/>
-    </row>
-    <row r="21" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A21" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="11"/>
-    </row>
-    <row r="22" spans="1:4" ht="57.75" customHeight="1">
-      <c r="A22" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
-    </row>
-    <row r="23" spans="1:4" ht="47.25" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="63"/>
-    </row>
-    <row r="67" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" ht="16.350000000000001" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:D6"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{35DD9789-9526-4404-AFBA-7AB05EA5049B}"/>
-    <hyperlink ref="D5" r:id="rId2" xr:uid="{80D32C04-12F5-4724-A269-AD00AFBFBAF4}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A09BCF3C-5DB1-4243-B7E5-CA690484534A}">
   <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
@@ -2613,7 +2282,7 @@
         <v>12</v>
       </c>
       <c r="B1" s="57" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C1" s="58"/>
       <c r="D1" s="59"/>
@@ -2624,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="60" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C2" s="60"/>
       <c r="D2" s="60"/>
@@ -2660,7 +2329,7 @@
       </c>
       <c r="B5" s="56"/>
       <c r="C5" s="14" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>22</v>
@@ -2681,7 +2350,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="41" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C7" s="42"/>
       <c r="D7" s="43"/>
@@ -2692,7 +2361,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C8" s="45"/>
       <c r="D8" s="46"/>
@@ -2752,38 +2421,36 @@
     </row>
     <row r="15" spans="1:5" ht="409.5" customHeight="1">
       <c r="A15" s="19" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C15" s="31"/>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:5" ht="246.75" customHeight="1">
       <c r="A16" s="19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C16" s="31"/>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="228.75" customHeight="1">
       <c r="A17" s="19" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C17" s="31"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="129" customHeight="1">
-      <c r="A18" s="19" t="s">
-        <v>84</v>
-      </c>
+      <c r="A18" s="19"/>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
       <c r="D18" s="3"/>
@@ -2858,257 +2525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594FFED9-EA5A-4E2C-AF57-DA80A94A4B41}">
-  <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="34.28515625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A1" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="57" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" ht="49.5" customHeight="1">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="60" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" ht="36" customHeight="1">
-      <c r="A3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A4" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" ht="75.75" customHeight="1">
-      <c r="A5" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" ht="29.1" customHeight="1">
-      <c r="A6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" ht="39.75" customHeight="1">
-      <c r="A7" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" ht="26.1" customHeight="1">
-      <c r="A8" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A9" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
-    </row>
-    <row r="10" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A10" s="38" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="27" customHeight="1">
-      <c r="A13" s="40"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="27" customHeight="1">
-      <c r="A14" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" spans="1:5" ht="186.75" customHeight="1">
-      <c r="A15" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" ht="144.75" customHeight="1">
-      <c r="A16" s="19"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" ht="127.5" customHeight="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" ht="88.5" customHeight="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" ht="36.75" customHeight="1">
-      <c r="A19" s="3"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A20" s="16"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="63"/>
-      <c r="D20" s="16"/>
-    </row>
-    <row r="21" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A21" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="11"/>
-    </row>
-    <row r="22" spans="1:4" ht="57.75" customHeight="1">
-      <c r="A22" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
-    </row>
-    <row r="23" spans="1:4" ht="47.25" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="63"/>
-    </row>
-    <row r="67" ht="17.850000000000001" customHeight="1"/>
-    <row r="68" ht="16.350000000000001" customHeight="1"/>
-    <row r="69" ht="16.350000000000001" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A6:D6"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{F7CB4800-8249-4A1A-8690-D0B2B7B7B3F2}"/>
-    <hyperlink ref="D5" r:id="rId2" xr:uid="{27EC3B11-C180-4595-B942-AF9225E26E3F}"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57CA40A-A83D-4543-9574-EB0713CAEC8D}">
   <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3422,9 +2839,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E377E60-00EF-4FC4-80A9-364CE34D49E2}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -3433,87 +2850,99 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="D7" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="D8" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="D9" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="D10" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7">
+      <c r="D18" s="68"/>
+      <c r="E18" s="68" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="68" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="68" t="s">
         <v>90</v>
       </c>
     </row>

--- a/тест-сьют.xlsx
+++ b/тест-сьют.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestProjectIntern_n1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE41CB32-093F-4F3B-81E0-AF0898A28374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430594C2-8671-4885-A19A-118CA6A35CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Тест-кейс №1" sheetId="4" r:id="rId1"/>
@@ -18,8 +18,17 @@
     <sheet name="Тест-кейс №3" sheetId="11" r:id="rId3"/>
     <sheet name="Тест-кейс №4" sheetId="13" r:id="rId4"/>
     <sheet name="Тест-кейс №5" sheetId="16" r:id="rId5"/>
-    <sheet name="Лист2" sheetId="9" r:id="rId6"/>
-    <sheet name="Лист1" sheetId="12" r:id="rId7"/>
+    <sheet name="Тест-кейс №6" sheetId="17" r:id="rId6"/>
+    <sheet name="Тест-кейс №7" sheetId="24" r:id="rId7"/>
+    <sheet name="Тест-кейс №8" sheetId="18" r:id="rId8"/>
+    <sheet name="Тест-кейс №9" sheetId="20" r:id="rId9"/>
+    <sheet name="Тест-кейс №10" sheetId="21" r:id="rId10"/>
+    <sheet name="Тест-кейс №11" sheetId="22" r:id="rId11"/>
+    <sheet name="Тест-кейс №12" sheetId="23" r:id="rId12"/>
+    <sheet name="Лист5" sheetId="19" r:id="rId13"/>
+    <sheet name="Лист2" sheetId="9" r:id="rId14"/>
+    <sheet name="Лист1" sheetId="12" r:id="rId15"/>
+    <sheet name="Лист11" sheetId="25" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="148">
   <si>
     <t>Название:</t>
   </si>
@@ -349,9 +358,6 @@
       </rPr>
       <t xml:space="preserve">  пользователя, то есть пользователь не должен быть зарегистрирован</t>
     </r>
-  </si>
-  <si>
-    <t>POST запрос со статусом 400, токен получен</t>
   </si>
   <si>
     <r>
@@ -417,11 +423,6 @@
     <t>1. Вызвать endpoint PUT https://itester.online/api/operations с body состоящим из {"operationCode":"AccountOpen"}</t>
   </si>
   <si>
-    <t>2. Вызвать endpoint PUTCH https://itester.online/api/operations?requestId (requestId берем из PUT запроса) с body состоящим из [
-    {"identifier":"AccountType","value":"string"},{"identifier":"Currency","value":"string"},{"identifier":"LastName","value":"string"},{"identifier":"FirstName","value":"string"},{"identifier":"MiddleName","value":"string"},{"identifier":"Birthdate","value":"string"}
-]</t>
-  </si>
-  <si>
     <t>3. Вызвать endpoint POST https://itester.online/api/operations?requestId (requestId берем из PUT запроса)</t>
   </si>
   <si>
@@ -485,19 +486,6 @@
 }</t>
   </si>
   <si>
-    <t>PUTCH запрос со статусом 200, получен response объект:{
-  "clientId": 0,
-  "isConfirmed": false,
-  "isFinished": true,
-  "name": "string",
-  "operationCode": "AccountOpen",
-  "requestId": 0,
-  "startDate": "string",
-  "stepId": 0,
-  "stepParams": null
-}</t>
-  </si>
-  <si>
     <t>POST запрос со статусом 200, получен response объект:{
   "clientId": 0,
   "isConfirmed": true,
@@ -519,17 +507,307 @@
   <si>
     <t>-0,01</t>
   </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>Открытие счета(Web-Api,негативный сценарий)</t>
+  </si>
+  <si>
+    <t>PUT запрос со статусом 400, получен response объект:
+{
+    "type": "https://tools.ietf.org/html/rfc9110#section-15.5.1",
+    "title": "One or more validation errors occurred.",
+    "status": 400,
+    "errors": {
+        "$.operationCode": [
+            "The JSON value could not be converted to iTester.Platform.Microservice.Platform.Contracts.Types.OperationCode. Path: $.operationCode | LineNumber: 2 | BytePositionInLine: 35."
+        ]
+    },
+    "traceId": string
+}</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>2. Вызвать endpoint PATCH https://itester.online/api/operations?requestId (requestId берем из PUT запроса) с body состоящим из [
+    {"identifier":"AccountType","value":"string"},{"identifier":"Currency","value":"string"},{"identifier":"LastName","value":"string"},{"identifier":"FirstName","value":"string"},{"identifier":"MiddleName","value":"string"},{"identifier":"Birthdate","value":"string"}
+]</t>
+  </si>
+  <si>
+    <t>PATCH запрос со статусом 200, получен response объект:{
+  "clientId": 0,
+  "isConfirmed": false,
+  "isFinished": true,
+  "name": "string",
+  "operationCode": "AccountOpen",
+  "requestId": 0,
+  "startDate": "string",
+  "stepId": 0,
+  "stepParams": null
+}</t>
+  </si>
+  <si>
+    <t>2. Вызвать endpoint PATCH https://itester.online/api/operations?requestId (requestId берем из PUT запроса) с body состоящим из [
+    {"identifier":"AccountType","value":"string"},{"identifier":"Currency","value":"Белорусский рубль"},{"identifier":"LastName","value":"string"},{"identifier":"FirstName","value":"string"},{"identifier":"MiddleName","value":"string"},{"identifier":"Birthdate","value":"string"}
+]</t>
+  </si>
+  <si>
+    <t>PATCH запрос со статусом 400, получено сообщение: "Неизвестная валюта"</t>
+  </si>
+  <si>
+    <t>POST запрос со статусом 500, получено сообщение:
+"Sequence contains no matching element"</t>
+  </si>
+  <si>
+    <t>Заказ карты(Web-Api,позитивный сценарий)</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/api/operations с body состоящим из {"operationCode":"CardOrder"}</t>
+  </si>
+  <si>
+    <t>PUT запрос со статусом 200, получен response объект:{
+  "clientId": 0,
+  "isConfirmed": false,
+  "isFinished": false,
+  "name": "string",
+  "operationCode": "CardOrder",
+  "requestId": 0,
+  "startDate": "string",
+  "stepId": 0,
+  "stepParams": [
+    {
+      "identifier": "string",
+      "value": "string",
+      "name": "string",
+      "requirements": {
+        "mask": "string",
+        "max": 0,
+        "min": 0,
+        "required": true
+      },
+      "type": "string",
+      "values": [
+        "string"
+      ]
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>PATCH запрос со статусом 200, получен response объект:{
+  "clientId": 0,
+  "isConfirmed": false,
+  "isFinished": true,
+  "name": "string",
+  "operationCode": "CardOrder",
+  "requestId": 0,
+  "startDate": "string",
+  "stepId": 0,
+  "stepParams": null
+}</t>
+  </si>
+  <si>
+    <t>POST запрос со статусом 200, получен response объект:{
+  "clientId": 0,
+  "isConfirmed": true,
+  "isFinished": true,
+  "name": "string",
+  "operationCode": "CardOrder",
+  "requestId": 0,
+  "startDate": "string",
+  "stepId": 0,
+  "stepParams": null
+}</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Заказ карты(Web-Api, негативный сценарий)</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/api/operations с body, где проверяется обработка каждого значения: {"operationCode":"fege"}
+{"operationCode":""}
+{"operationCode":"null"}
+{"operationCode":null}
+{"operationCode":"&amp;*#&amp;@-"}</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/api/operations с body, где проверяется обработка каждого значения: {"operationCode":"fege"}
+{"operationCode":"1"}
+{"operationCode":"0"}
+{"operationCode":"-1'}</t>
+  </si>
+  <si>
+    <t>PUT запрос со статусом 500, получено сообщение: 
+"Value cannot be null. (Parameter 'name')"</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>Заказ карты(Web-Api,негативный сценарий)</t>
+  </si>
+  <si>
+    <t>2. Вызвать endpoint PATCH https://itester.online/api/operations?requestId (requestId берем из PUT запроса) с body состоящим из [
+    {"identifier":"AccountType","value":"string"},{"identifier":"Currency","value":"string"},{"identifier":"LastName","value":"string"},{"identifier":"FirstName","value":"string"},{"identifier":"MiddleName","value":"string"},{"identifier":"Birthdate","value":"string"}
+]
+где проверяется обработка таких значений 
+[
+  [
+    {"identifier":"Product","value":"Золотая карта"},
+    {"identifier":"ProgramType","value":"Mastercard"}
+  ],
+  [
+    {"identifier":"Product","value":"Дебетовая карта"},
+    {"identifier":"ProgramType","value":"Т‑банк"}
+  ],
+  [
+    {"identifier":"Product","value":""},
+    {"identifier":"ProgramType","value":"Mastercard"}
+  ],
+  [
+    {"identifier":"Product","value":"Дебетовая карта"},
+    {"identifier":"ProgramType","value":""}
+  ]
+]</t>
+  </si>
+  <si>
+    <t>PATCH запрос со статусом 400</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint PUT https://itester.online/api/operations с body, де проверяется обработка каждого значения: {"operationCode":"HDiirn"}
+{"operationCode":""}
+{"operationCode":"null"}
+{"operationCode":null}
+{"operationCode":"&amp;*#&amp;@-"}</t>
+  </si>
+  <si>
+    <t>Открытие счета(Web-Api, негативный сценарий)</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>"число"</t>
+  </si>
+  <si>
+    <t>Может быть:</t>
+  </si>
+  <si>
+    <t>Не может быть:</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>"null"</t>
+  </si>
+  <si>
+    <t>""</t>
+  </si>
+  <si>
+    <t>"любое другое слово"</t>
+  </si>
+  <si>
+    <t>"male"</t>
+  </si>
+  <si>
+    <t>"female"</t>
+  </si>
+  <si>
+    <t>"Male"</t>
+  </si>
+  <si>
+    <t>"Female"</t>
+  </si>
+  <si>
+    <t>"MALE"</t>
+  </si>
+  <si>
+    <t>"FEMALE"</t>
+  </si>
+  <si>
+    <t>birthdate</t>
+  </si>
+  <si>
+    <t>DD.MM.YY</t>
+  </si>
+  <si>
+    <t>YY-MM-DD</t>
+  </si>
+  <si>
+    <t>DD-MM-YY</t>
+  </si>
+  <si>
+    <t>"@#$$#"</t>
+  </si>
+  <si>
+    <t>"dsdvvsv"</t>
+  </si>
+  <si>
+    <t>sdsds@yandex.ru</t>
+  </si>
+  <si>
+    <t>проще говоря нет проверки на сам эмейл</t>
+  </si>
+  <si>
+    <t>число</t>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">только </t>
+  </si>
+  <si>
+    <t>Пустой эмейл и новый логин отправить нельзя</t>
+  </si>
+  <si>
+    <t>добавить тест с неправ токеном</t>
+  </si>
+  <si>
+    <t>cookie X-iTester-Access: 2ad3f9a0ee6b486db902ade89d6850ff</t>
+  </si>
+  <si>
+    <t>1. Вызвать endpoint POST https://itester.online/api/authorization/token c body состоящим из несуществующего login и password</t>
+  </si>
+  <si>
+    <t>POST запрос со статусом 400</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -599,8 +877,14 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -634,6 +918,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -809,81 +1111,81 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -892,125 +1194,168 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1253,40 +1598,40 @@
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="49.5" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="36" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="54"/>
+      <c r="B4" s="58"/>
       <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
@@ -1296,10 +1641,10 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="75.75" customHeight="1">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="56"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="14" t="s">
         <v>21</v>
       </c>
@@ -1309,74 +1654,74 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="29.1" customHeight="1">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="39.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="26.1" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="24.95" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
     </row>
     <row r="10" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
       <c r="D11" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
       <c r="D12" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
-      <c r="A13" s="40"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
       <c r="D13" s="7" t="s">
         <v>11</v>
       </c>
@@ -1393,10 +1738,10 @@
       <c r="A15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="31"/>
+      <c r="C15" s="61"/>
       <c r="D15" s="2" t="s">
         <v>61</v>
       </c>
@@ -1405,10 +1750,10 @@
       <c r="A16" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="61" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="31"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="2" t="s">
         <v>61</v>
       </c>
@@ -1417,30 +1762,30 @@
       <c r="A17" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="31"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="34.5" customHeight="1">
       <c r="A18" s="3"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="63"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
       <c r="A19" s="3"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="63"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
       <c r="A20" s="16"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="63"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="16"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1">
@@ -1455,23 +1800,26 @@
       <c r="A22" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
     </row>
     <row r="23" spans="1:4" ht="47.25" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="63"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
     </row>
     <row r="67" ht="17.850000000000001" customHeight="1"/>
     <row r="68" ht="16.350000000000001" customHeight="1"/>
     <row r="69" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="A10:A13"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B23:D23"/>
@@ -1488,9 +1836,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B10:C13"/>
-    <mergeCell ref="A10:A13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{3BDBCFF2-7F58-4390-895F-68E37F2E0168}"/>
@@ -1498,6 +1843,1382 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D9EAF4-5AA8-48A3-817B-B3AE936633C6}">
+  <dimension ref="A1:E69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="37.5" customHeight="1">
+      <c r="A4" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" ht="75.75" customHeight="1">
+      <c r="A5" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="29.1" customHeight="1">
+      <c r="A6" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="39.75" customHeight="1">
+      <c r="A7" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="26.1" customHeight="1">
+      <c r="A8" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A9" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+    </row>
+    <row r="10" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A10" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1">
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.5" customHeight="1">
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27" customHeight="1">
+      <c r="A14" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:5" ht="409.5" customHeight="1">
+      <c r="A15" s="31" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="246.75" customHeight="1">
+      <c r="A16" s="31"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="228.75" customHeight="1">
+      <c r="A17" s="31"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="129" customHeight="1">
+      <c r="A18" s="31"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="16"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A21" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
+    </row>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+    </row>
+    <row r="67" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{8D7B6597-D5B2-4AD2-9F8C-E7160AF351A0}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{2DD49A83-E2E9-4C83-9AC7-266F5373534A}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B58B8634-B51E-4A8B-B4F1-81FB30541976}">
+  <dimension ref="A1:E69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="37.5" customHeight="1">
+      <c r="A4" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" ht="75.75" customHeight="1">
+      <c r="A5" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="29.1" customHeight="1">
+      <c r="A6" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="39.75" customHeight="1">
+      <c r="A7" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="26.1" customHeight="1">
+      <c r="A8" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A9" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+    </row>
+    <row r="10" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A10" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1">
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.5" customHeight="1">
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27" customHeight="1">
+      <c r="A14" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:5" ht="409.5" customHeight="1">
+      <c r="A15" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="73"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="246.75" customHeight="1">
+      <c r="A16" s="31"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="228.75" customHeight="1">
+      <c r="A17" s="31"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="129" customHeight="1">
+      <c r="A18" s="31"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="16"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A21" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
+    </row>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+    </row>
+    <row r="67" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{81BD7B4E-35AA-4DCB-B787-178F0F29498E}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{F51BE038-6487-4C46-A057-93A485D1A271}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{394969A7-4B8A-4304-8EC4-5395CBE75F3A}">
+  <dimension ref="A1:E69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="37.5" customHeight="1">
+      <c r="A4" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" ht="75.75" customHeight="1">
+      <c r="A5" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="29.1" customHeight="1">
+      <c r="A6" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="39.75" customHeight="1">
+      <c r="A7" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="26.1" customHeight="1">
+      <c r="A8" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A9" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+    </row>
+    <row r="10" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A10" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1">
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.5" customHeight="1">
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27" customHeight="1">
+      <c r="A14" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:5" ht="409.5" customHeight="1">
+      <c r="A15" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="408.75" customHeight="1">
+      <c r="A16" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="61"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="228.75" customHeight="1">
+      <c r="A17" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="61"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="129" customHeight="1">
+      <c r="A18" s="31"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="16"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A21" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
+    </row>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+    </row>
+    <row r="67" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{82724F81-2E7C-47A4-B63D-E9131B3698E1}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{894222DF-4B82-4156-B3B4-6F7BCE85B4E1}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{192F95AD-2CDD-4EB1-A66D-CA8BBDDDC081}">
+  <dimension ref="C2:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="25.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" customWidth="1"/>
+    <col min="10" max="10" width="31" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="13" max="13" width="25.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:13">
+      <c r="C2" s="77" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="77"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="82" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="77"/>
+      <c r="I2" s="82" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="77"/>
+      <c r="L2" s="82" t="s">
+        <v>141</v>
+      </c>
+      <c r="M2" s="77"/>
+    </row>
+    <row r="3" spans="3:13">
+      <c r="C3" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="78" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="78" t="s">
+        <v>121</v>
+      </c>
+      <c r="I3" s="76" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="78" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="3:13">
+      <c r="C4" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="80" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="80" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="I4" s="86" t="s">
+        <v>137</v>
+      </c>
+      <c r="J4" s="80" t="s">
+        <v>140</v>
+      </c>
+      <c r="M4" s="83" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="3:13">
+      <c r="C5" s="80" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" s="80" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="80" t="s">
+        <v>133</v>
+      </c>
+      <c r="I5" s="86" t="s">
+        <v>124</v>
+      </c>
+      <c r="L5" s="75" t="s">
+        <v>142</v>
+      </c>
+      <c r="M5" s="75" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="3:13">
+      <c r="C6" s="80" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="80" t="s">
+        <v>125</v>
+      </c>
+      <c r="G6" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="I6" s="86" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="3:13">
+      <c r="C7" s="80" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" s="80" t="s">
+        <v>124</v>
+      </c>
+      <c r="G7" s="84" t="s">
+        <v>136</v>
+      </c>
+      <c r="I7" s="86" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="3:13">
+      <c r="C8" s="80" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" s="84" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="80" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" s="86" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="3:13">
+      <c r="C9" s="81" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="10" spans="3:13">
+      <c r="C10" s="81" t="s">
+        <v>131</v>
+      </c>
+      <c r="I10" s="85" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="3:13" ht="30">
+      <c r="I11" s="87" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="3:13" ht="45">
+      <c r="L12" s="87" t="s">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="L2:M2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="I10" r:id="rId1" xr:uid="{44BBE22B-4AA8-451A-974C-11E1A7F6B631}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57CA40A-A83D-4543-9574-EB0713CAEC8D}">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="5" width="52.5703125" customWidth="1"/>
+    <col min="6" max="18" width="30.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A1" s="21"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+    </row>
+    <row r="2" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="21">
+        <v>1</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="22">
+        <v>79786985898</v>
+      </c>
+      <c r="F2" s="25"/>
+    </row>
+    <row r="3" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A3" s="21"/>
+      <c r="B3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="21">
+        <v>2</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="26"/>
+    </row>
+    <row r="4" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A4" s="21"/>
+      <c r="B4" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="21">
+        <v>3</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="26"/>
+    </row>
+    <row r="5" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21">
+        <v>4</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="26"/>
+    </row>
+    <row r="6" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21">
+        <v>5</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="26"/>
+    </row>
+    <row r="7" spans="1:10" ht="78" customHeight="1">
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21">
+        <v>6</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="52.5" customHeight="1">
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21">
+        <v>7</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="21"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21">
+        <v>8</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="27"/>
+    </row>
+    <row r="10" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21">
+        <v>9</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="27"/>
+    </row>
+    <row r="11" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21">
+        <v>10</v>
+      </c>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="27"/>
+    </row>
+    <row r="12" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+    </row>
+    <row r="13" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+    </row>
+    <row r="14" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A15" s="21"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="39.950000000000003" customHeight="1">
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J16" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="8:10" ht="39.950000000000003" customHeight="1">
+      <c r="H17" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="8:10" ht="39.950000000000003" customHeight="1">
+      <c r="H18" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="8:10" ht="39.950000000000003" customHeight="1">
+      <c r="H19" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="8:10" ht="39.950000000000003" customHeight="1">
+      <c r="H20" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="8:10" ht="39.950000000000003" customHeight="1">
+      <c r="H21" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="8:10" ht="51.75" customHeight="1">
+      <c r="H22" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{B91D3E45-368F-4F04-B08B-5245F5531497}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E377E60-00EF-4FC4-80A9-364CE34D49E2}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="D7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="D8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="D10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="4:7">
+      <c r="D18" s="34"/>
+      <c r="E18" s="34" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>86</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{771EF6D3-C353-4422-BD8A-F537BDD99C41}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1517,40 +3238,40 @@
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="49.5" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="36" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="54"/>
+      <c r="B4" s="58"/>
       <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
@@ -1560,10 +3281,10 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="75.75" customHeight="1">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="56"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="14" t="s">
         <v>21</v>
       </c>
@@ -1573,74 +3294,74 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="29.1" customHeight="1">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="39.75" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="26.1" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="24.95" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
     </row>
     <row r="10" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
       <c r="D11" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
       <c r="D12" s="13" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
-      <c r="A13" s="40"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
       <c r="D13" s="13" t="s">
         <v>11</v>
       </c>
@@ -1657,42 +3378,42 @@
       <c r="A15" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="31"/>
+      <c r="C15" s="61"/>
       <c r="D15" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="87.75" customHeight="1">
       <c r="A16" s="13"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="35.1" customHeight="1">
       <c r="A17" s="8"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="67"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="34.5" customHeight="1">
       <c r="A18" s="3"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="63"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
       <c r="A19" s="3"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="63"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
       <c r="A20" s="16"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="63"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="16"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1">
@@ -1707,17 +3428,534 @@
       <c r="A22" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
     </row>
     <row r="23" spans="1:4" ht="47.25" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="63"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+    </row>
+    <row r="67" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{7A4F2634-6B90-43AB-923D-FAE6F97EA998}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{2BD9F5B5-1612-406E-9C1B-537CE7D2A13D}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FE49A0-26A4-4FC9-8BCE-B5A0D8887350}">
+  <dimension ref="A1:E69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="37.5" customHeight="1">
+      <c r="A4" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" ht="75.75" customHeight="1">
+      <c r="A5" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="29.1" customHeight="1">
+      <c r="A6" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="39.75" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="26.1" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="48"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+    </row>
+    <row r="10" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A10" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1">
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.5" customHeight="1">
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27" customHeight="1">
+      <c r="A14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:5" ht="186.75" customHeight="1">
+      <c r="A15" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="144.75" customHeight="1">
+      <c r="A16" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="61"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="127.5" customHeight="1">
+      <c r="A17" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="61"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="88.5" customHeight="1">
+      <c r="A18" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="61" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="61"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="16"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A21" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
+    </row>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+    </row>
+    <row r="67" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" ht="16.350000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{CCE46329-C7AE-4AE0-9332-C437BCE367D4}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{82918AF3-6ADC-4608-A95E-C7416F45FA36}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C64A4486-FE92-44AA-9CA5-0E190E1C6006}">
+  <dimension ref="A1:E69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="37.5" customHeight="1">
+      <c r="A4" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" ht="75.75" customHeight="1">
+      <c r="A5" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="29.1" customHeight="1">
+      <c r="A6" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="39.75" customHeight="1">
+      <c r="A7" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="26.1" customHeight="1">
+      <c r="A8" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A9" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+    </row>
+    <row r="10" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A10" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1">
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.5" customHeight="1">
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27" customHeight="1">
+      <c r="A14" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:5" ht="186.75" customHeight="1">
+      <c r="A15" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="75" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="144.75" customHeight="1">
+      <c r="A16" s="19"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="127.5" customHeight="1">
+      <c r="A17" s="19"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="88.5" customHeight="1">
+      <c r="A18" s="19"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="16"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A21" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
+    </row>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
     </row>
     <row r="67" ht="17.850000000000001" customHeight="1"/>
     <row r="68" ht="16.350000000000001" customHeight="1"/>
@@ -1745,22 +3983,22 @@
     <mergeCell ref="B22:D22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{7A4F2634-6B90-43AB-923D-FAE6F97EA998}"/>
-    <hyperlink ref="D5" r:id="rId2" xr:uid="{2BD9F5B5-1612-406E-9C1B-537CE7D2A13D}"/>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{27B05CB2-784A-44F1-AFCC-8C8235586D6E}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{AEF0CF09-1207-4A6C-8124-DCCBBA7D1957}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96FE49A0-26A4-4FC9-8BCE-B5A0D8887350}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A09BCF3C-5DB1-4243-B7E5-CA690484534A}">
   <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" customWidth="1"/>
     <col min="4" max="4" width="41.85546875" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
@@ -1769,40 +4007,40 @@
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="57" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
+      <c r="B1" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="49.5" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="60" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="B2" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="36" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="54"/>
+      <c r="B4" s="58"/>
       <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
@@ -1812,12 +4050,12 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="75.75" customHeight="1">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="56"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="14" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>22</v>
@@ -1825,140 +4063,138 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="29.1" customHeight="1">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="39.75" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
+      <c r="B7" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="26.1" customHeight="1">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
+      <c r="B8" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
     </row>
     <row r="10" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="13" t="s">
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="19" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="13" t="s">
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="19" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
-      <c r="A13" s="40"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="13" t="s">
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="19" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
     </row>
-    <row r="15" spans="1:5" ht="186.75" customHeight="1">
-      <c r="A15" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="31"/>
+    <row r="15" spans="1:5" ht="409.5" customHeight="1">
+      <c r="A15" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="61"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:5" ht="144.75" customHeight="1">
-      <c r="A16" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="31"/>
+    <row r="16" spans="1:5" ht="246.75" customHeight="1">
+      <c r="A16" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="61"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" ht="127.5" customHeight="1">
-      <c r="A17" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="31"/>
+    <row r="17" spans="1:4" ht="228.75" customHeight="1">
+      <c r="A17" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="61"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" ht="88.5" customHeight="1">
-      <c r="A18" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="31"/>
+    <row r="18" spans="1:4" ht="129" customHeight="1">
+      <c r="A18" s="19"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
       <c r="A19" s="3"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="63"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
       <c r="A20" s="16"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="63"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="16"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="18" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="10"/>
@@ -1969,17 +4205,17 @@
       <c r="A22" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
     </row>
     <row r="23" spans="1:4" ht="47.25" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="63"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
     </row>
     <row r="67" ht="17.850000000000001" customHeight="1"/>
     <row r="68" ht="16.350000000000001" customHeight="1"/>
@@ -2007,22 +4243,22 @@
     <mergeCell ref="B22:D22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{CCE46329-C7AE-4AE0-9332-C437BCE367D4}"/>
-    <hyperlink ref="D5" r:id="rId2" xr:uid="{82918AF3-6ADC-4608-A95E-C7416F45FA36}"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{D54C3230-B9DC-49E5-999B-2E3DF3181363}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{48ABB421-73B1-4D1D-9427-6C6B8C688C80}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C64A4486-FE92-44AA-9CA5-0E190E1C6006}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BC468D-0C46-4A0F-B2F2-E0049C0161E7}">
   <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34.28515625" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" customWidth="1"/>
     <col min="4" max="4" width="41.85546875" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
@@ -2031,40 +4267,40 @@
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
+      <c r="B1" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="49.5" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="B2" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="36" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="54"/>
+      <c r="B4" s="58"/>
       <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
@@ -2074,12 +4310,12 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="75.75" customHeight="1">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="56"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="14" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>22</v>
@@ -2087,128 +4323,130 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="29.1" customHeight="1">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="39.75" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
+      <c r="B7" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="26.1" customHeight="1">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
+      <c r="B8" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
     </row>
     <row r="10" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="19" t="s">
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="31" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="19" t="s">
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="31" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
-      <c r="A13" s="40"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="19" t="s">
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" customHeight="1">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="32" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="11"/>
     </row>
-    <row r="15" spans="1:5" ht="186.75" customHeight="1">
-      <c r="A15" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="31"/>
+    <row r="15" spans="1:5" ht="409.5" customHeight="1">
+      <c r="A15" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="61"/>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:5" ht="144.75" customHeight="1">
-      <c r="A16" s="19"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
+    <row r="16" spans="1:5" ht="246.75" customHeight="1">
+      <c r="A16" s="31"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="2"/>
     </row>
-    <row r="17" spans="1:4" ht="127.5" customHeight="1">
-      <c r="A17" s="19"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="31"/>
+    <row r="17" spans="1:4" ht="228.75" customHeight="1">
+      <c r="A17" s="31"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" ht="88.5" customHeight="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
+    <row r="18" spans="1:4" ht="129" customHeight="1">
+      <c r="A18" s="31"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
       <c r="A19" s="3"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="63"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
       <c r="A20" s="16"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="63"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="16"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="32" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="10"/>
@@ -2219,17 +4457,17 @@
       <c r="A22" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
     </row>
     <row r="23" spans="1:4" ht="47.25" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="63"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
     </row>
     <row r="67" ht="17.850000000000001" customHeight="1"/>
     <row r="68" ht="16.350000000000001" customHeight="1"/>
@@ -2257,16 +4495,16 @@
     <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" xr:uid="{27B05CB2-784A-44F1-AFCC-8C8235586D6E}"/>
-    <hyperlink ref="C5" r:id="rId2" xr:uid="{AEF0CF09-1207-4A6C-8124-DCCBBA7D1957}"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{0C7A0809-A876-44EB-80A5-FB00F61A0774}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{AFD14694-3F77-49F3-92E3-0F001D8D862A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A09BCF3C-5DB1-4243-B7E5-CA690484534A}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C914DDD-3652-4E23-950E-79F76CF877E0}">
   <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -2281,40 +4519,40 @@
       <c r="A1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="58"/>
-      <c r="D1" s="59"/>
+      <c r="B1" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" ht="49.5" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="B2" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" ht="36" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="52"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="54"/>
+      <c r="B4" s="58"/>
       <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
@@ -2324,12 +4562,12 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" ht="75.75" customHeight="1">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="56"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>22</v>
@@ -2337,82 +4575,82 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" ht="29.1" customHeight="1">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="49"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" ht="39.75" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="42"/>
-      <c r="D7" s="43"/>
+      <c r="B7" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" ht="26.1" customHeight="1">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="44" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
+      <c r="B8" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
       <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" ht="24.95" customHeight="1">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
     </row>
     <row r="10" spans="1:5" ht="35.1" customHeight="1">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="33"/>
+      <c r="C10" s="63"/>
       <c r="D10" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="19" t="s">
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="31" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A12" s="39"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="19" t="s">
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="31" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="27" customHeight="1">
-      <c r="A13" s="40"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="19" t="s">
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="31" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="27" customHeight="1">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="32" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="10"/>
@@ -2420,55 +4658,47 @@
       <c r="D14" s="11"/>
     </row>
     <row r="15" spans="1:5" ht="409.5" customHeight="1">
-      <c r="A15" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="31"/>
+      <c r="A15" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="73"/>
       <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:5" ht="246.75" customHeight="1">
-      <c r="A16" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="31"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
       <c r="D16" s="2"/>
     </row>
     <row r="17" spans="1:4" ht="228.75" customHeight="1">
-      <c r="A17" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="31"/>
+      <c r="A17" s="31"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" ht="129" customHeight="1">
-      <c r="A18" s="19"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
+      <c r="A18" s="31"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" ht="36.75" customHeight="1">
       <c r="A19" s="3"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="63"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
       <c r="D19" s="3"/>
     </row>
     <row r="20" spans="1:4" ht="34.5" customHeight="1">
       <c r="A20" s="16"/>
-      <c r="B20" s="61"/>
-      <c r="C20" s="63"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
       <c r="D20" s="16"/>
     </row>
     <row r="21" spans="1:4" ht="40.5" customHeight="1">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="32" t="s">
         <v>8</v>
       </c>
       <c r="B21" s="10"/>
@@ -2479,17 +4709,17 @@
       <c r="A22" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
-      <c r="D22" s="66"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
     </row>
     <row r="23" spans="1:4" ht="47.25" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="63"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
     </row>
     <row r="67" ht="17.850000000000001" customHeight="1"/>
     <row r="68" ht="16.350000000000001" customHeight="1"/>
@@ -2517,436 +4747,530 @@
     <mergeCell ref="A6:D6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{D54C3230-B9DC-49E5-999B-2E3DF3181363}"/>
-    <hyperlink ref="D5" r:id="rId2" xr:uid="{48ABB421-73B1-4D1D-9427-6C6B8C688C80}"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{3075D3F0-9E87-44C4-9690-37462C3B3410}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{FEEF3DB6-4AF0-4C16-A4B8-B467791DBB9B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C57CA40A-A83D-4543-9574-EB0713CAEC8D}">
-  <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA430FA1-23E4-4677-9703-926520B70A5E}">
+  <dimension ref="A1:E69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="52.5703125" customWidth="1"/>
-    <col min="6" max="18" width="30.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="21"/>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-    </row>
-    <row r="2" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="21">
+    <row r="1" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="37.5" customHeight="1">
+      <c r="A4" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" ht="75.75" customHeight="1">
+      <c r="A5" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="29.1" customHeight="1">
+      <c r="A6" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="22">
-        <v>79786985898</v>
-      </c>
-      <c r="F2" s="25"/>
-    </row>
-    <row r="3" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="21"/>
-      <c r="B3" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="21">
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="39.75" customHeight="1">
+      <c r="A7" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="26"/>
-    </row>
-    <row r="4" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A4" s="21"/>
-      <c r="B4" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="21">
+      <c r="B7" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="26.1" customHeight="1">
+      <c r="A8" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="26"/>
-    </row>
-    <row r="5" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21">
+      <c r="B8" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A9" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="26"/>
-    </row>
-    <row r="6" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21">
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+    </row>
+    <row r="10" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A10" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="26"/>
-    </row>
-    <row r="7" spans="1:10" ht="78" customHeight="1">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21">
+      <c r="B10" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="21"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="52.5" customHeight="1">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21">
+      <c r="C10" s="63"/>
+      <c r="D10" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21">
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1">
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.5" customHeight="1">
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27" customHeight="1">
+      <c r="A14" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:5" ht="409.5" customHeight="1">
+      <c r="A15" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="246.75" customHeight="1">
+      <c r="A16" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="61"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="228.75" customHeight="1">
+      <c r="A17" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="61"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="129" customHeight="1">
+      <c r="A18" s="31"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="16"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A21" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="27"/>
-    </row>
-    <row r="10" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21">
-        <v>9</v>
-      </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="27"/>
-    </row>
-    <row r="11" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21">
-        <v>10</v>
-      </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="27"/>
-    </row>
-    <row r="12" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-    </row>
-    <row r="13" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-    </row>
-    <row r="14" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="39.950000000000003" customHeight="1">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="8:10" ht="39.950000000000003" customHeight="1">
-      <c r="H17" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="J17" s="24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="8:10" ht="39.950000000000003" customHeight="1">
-      <c r="H18" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="I18" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="8:10" ht="39.950000000000003" customHeight="1">
-      <c r="H19" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="I19" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="J19" s="24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="20" spans="8:10" ht="39.950000000000003" customHeight="1">
-      <c r="H20" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="I20" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="8:10" ht="39.950000000000003" customHeight="1">
-      <c r="H21" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="J21" s="24" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="8:10" ht="51.75" customHeight="1">
-      <c r="H22" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>47</v>
-      </c>
-    </row>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
+    </row>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+    </row>
+    <row r="67" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" xr:uid="{B91D3E45-368F-4F04-B08B-5245F5531497}"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{4E5BF265-372E-43D5-9BFE-A416437E25BE}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{04001D0C-4FE3-4A03-8362-4F2A40931623}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E377E60-00EF-4FC4-80A9-364CE34D49E2}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E2BB9BC-D557-45A6-AE1E-A7858ECBC789}">
+  <dimension ref="A1:E69"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="51.42578125" customWidth="1"/>
+    <col min="4" max="4" width="41.85546875" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="D7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="D10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="4:7">
-      <c r="D18" s="68"/>
-      <c r="E18" s="68" t="s">
-        <v>91</v>
-      </c>
-      <c r="F18" s="68" t="s">
-        <v>89</v>
-      </c>
-      <c r="G18" s="68" t="s">
-        <v>90</v>
-      </c>
-    </row>
+    <row r="1" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" ht="49.5" customHeight="1">
+      <c r="A2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="36" customHeight="1">
+      <c r="A3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" ht="37.5" customHeight="1">
+      <c r="A4" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="58"/>
+      <c r="C4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" ht="75.75" customHeight="1">
+      <c r="A5" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="60"/>
+      <c r="C5" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" ht="29.1" customHeight="1">
+      <c r="A6" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="39.75" customHeight="1">
+      <c r="A7" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="45" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" ht="26.1" customHeight="1">
+      <c r="A8" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" ht="24.95" customHeight="1">
+      <c r="A9" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="50"/>
+    </row>
+    <row r="10" spans="1:5" ht="35.1" customHeight="1">
+      <c r="A10" s="68" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1">
+      <c r="A11" s="69"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.5" customHeight="1">
+      <c r="A12" s="69"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27" customHeight="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27" customHeight="1">
+      <c r="A14" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="11"/>
+    </row>
+    <row r="15" spans="1:5" ht="409.5" customHeight="1">
+      <c r="A15" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="61"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" ht="246.75" customHeight="1">
+      <c r="A16" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="61"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" ht="228.75" customHeight="1">
+      <c r="A17" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="61" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="61"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" ht="129" customHeight="1">
+      <c r="A18" s="31"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" ht="36.75" customHeight="1">
+      <c r="A19" s="3"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A20" s="16"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="16"/>
+    </row>
+    <row r="21" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A21" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" ht="57.75" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="44"/>
+    </row>
+    <row r="23" spans="1:4" ht="47.25" customHeight="1">
+      <c r="A23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="39"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41"/>
+    </row>
+    <row r="67" ht="17.850000000000001" customHeight="1"/>
+    <row r="68" ht="16.350000000000001" customHeight="1"/>
+    <row r="69" ht="16.350000000000001" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="19">
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A6:D6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{B23EF7D4-4DF8-46BC-9260-7656332DB56B}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{BEA0A4A4-E803-4E2D-AB2B-B10BCA871146}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>